--- a/docs/xlsx/jobs-2026-09-27.xlsx
+++ b/docs/xlsx/jobs-2026-09-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="21">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,52 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Engagement &amp; Operations Assistant (part time)</t>
+  </si>
+  <si>
+    <t>Orion Magazine</t>
+  </si>
+  <si>
+    <t>Great Barrington, Massachusetts</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Animals, Arts Music, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/08acf0a5ca6242feba922f84e4333270-engagement-operations-assistant-part-time-orion-magazine-great-barrington</t>
+  </si>
+  <si>
+    <t>Executive Director/Fundraiser</t>
+  </si>
+  <si>
+    <t>The Vegan Museum</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 40.00/hour</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4c695d8eaf54c6ebc4439172cf06214-executive-directorfundraiser-the-vegan-museum-chicago</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +93,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +119,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +558,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +597,58 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-27.xlsx
+++ b/docs/xlsx/jobs-2026-09-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="54">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,45 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Board member position Human Resources Director</t>
+  </si>
+  <si>
+    <t>Veterans Group United Inc.</t>
+  </si>
+  <si>
+    <t>Remote (Florida)</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/33202ca219ca459c9c6a332384ad8394-board-member-position-human-resources-director-veterans-group-united-inc-yulee</t>
+  </si>
+  <si>
+    <t>Clean and Prosperous Executive Director</t>
+  </si>
+  <si>
+    <t>Clover Search Works</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 185000.00 - 215000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/603213abd4a143eaa1b8185ef7255e66-clean-and-prosperous-executive-director-clover-search-works-seattle</t>
+  </si>
+  <si>
     <t>Engagement &amp; Operations Assistant (part time)</t>
   </si>
   <si>
@@ -49,9 +88,6 @@
     <t>Great Barrington, Massachusetts</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 22.00 - 25.00/hour</t>
   </si>
   <si>
@@ -77,6 +113,69 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/f4c695d8eaf54c6ebc4439172cf06214-executive-directorfundraiser-the-vegan-museum-chicago</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Cypress Fund</t>
+  </si>
+  <si>
+    <t>Columbia, South Carolina</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6747b81d8a34437ab6ddda3e5e5b0e3d-operations-manager-cypress-fund-columbia</t>
+  </si>
+  <si>
+    <t>Raleigh, North Carolina</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/350e69a81c754e02af8f9a3c05cee7d9-operations-manager-cypress-fund-raleigh</t>
+  </si>
+  <si>
+    <t>People Operations Manager</t>
+  </si>
+  <si>
+    <t>Santa Cruz SPCA and Humane Society</t>
+  </si>
+  <si>
+    <t>Santa Cruz, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6033708213974035b3b73587a1af1641-people-operations-manager-santa-cruz-spca-and-humane-society-santa-cruz</t>
+  </si>
+  <si>
+    <t>Senior Staff Attorney, Temporary</t>
+  </si>
+  <si>
+    <t>Human Rights First</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d75c30895201441287402922935ef244-senior-staff-attorney-temporary-human-rights-first-new-york</t>
   </si>
 </sst>
 </file>
@@ -558,7 +657,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -631,16 +730,154 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -648,6 +885,12 @@
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
